--- a/devices.xlsx
+++ b/devices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soyel\OneDrive\Documents\Thermoguard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058C2C8F-A640-4CF3-B744-7371AF784F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFCB622-8BDF-4B86-B9AE-55EB67803F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="2700" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Devices" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="63">
   <si>
     <t>SERIAL_NUMBER</t>
   </si>
@@ -239,6 +239,15 @@
   </si>
   <si>
     <t>https://goodrest.thermoguard.bernard.com.ar/devices/08d17e1a-051e-44ad-b10a-2568641a1d8f</t>
+  </si>
+  <si>
+    <t>TEST-0104</t>
+  </si>
+  <si>
+    <t>70B3D57ED00728FF</t>
+  </si>
+  <si>
+    <t>AD5DA099427AB76C03591AD29893A1C6</t>
   </si>
 </sst>
 </file>
@@ -315,8 +324,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{371DA425-F10D-414C-933C-3F3A48044E36}" name="DEVICES_TABLE" displayName="DEVICES_TABLE" ref="A1:J16" totalsRowShown="0">
-  <autoFilter ref="A1:J16" xr:uid="{371DA425-F10D-414C-933C-3F3A48044E36}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{371DA425-F10D-414C-933C-3F3A48044E36}" name="DEVICES_TABLE" displayName="DEVICES_TABLE" ref="A1:J17" totalsRowShown="0">
+  <autoFilter ref="A1:J17" xr:uid="{371DA425-F10D-414C-933C-3F3A48044E36}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{DDFDFD3A-0F67-44BC-90CE-8508D1EEF5DF}" name="SERIAL_NUMBER"/>
     <tableColumn id="2" xr3:uid="{1850FEB3-A6F0-4B5C-BEFD-AEBFC49FCE8C}" name="DEV_EUI"/>
@@ -610,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -997,10 +1006,36 @@
         <v>54</v>
       </c>
     </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>104</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="E17">
+        <v>3.64</v>
+      </c>
+      <c r="F17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F16" xr:uid="{A2CB1A3C-BAF6-4008-8029-88D6EF68FAEB}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F17" xr:uid="{A2CB1A3C-BAF6-4008-8029-88D6EF68FAEB}">
       <formula1>INDIRECT("CLIENTS_TABLE[CLIENT_NAME]")</formula1>
     </dataValidation>
   </dataValidations>
@@ -1057,7 +1092,7 @@
       </c>
       <c r="C3">
         <f>COUNTIF(DEVICES_TABLE[CLIENT],"="&amp;CLIENTS_TABLE[[#This Row],[CLIENT_NAME]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
